--- a/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-empfindlichkeit-phenotyp-loinc.xlsx
+++ b/branches/v2027.0.0-ballot.rc1/ValueSet-mii-vs-mikrobio-empfindlichkeit-phenotyp-loinc.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -139,7 +139,7 @@
     <t>106843-6</t>
   </si>
   <si>
-    <t>Cefotaxime+Cloxacillin [Susceptibility] in Isolate by Broth dilution</t>
+    <t>Cefotaxime+Cloxacillin [Susceptibility] in Isolate by Disk diffusion (KB)</t>
   </si>
   <si>
     <t>103673-0</t>
